--- a/Empregos_por_Secao_CNAE_RAIS_Capanema.xlsx
+++ b/Empregos_por_Secao_CNAE_RAIS_Capanema.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:AF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -469,1625 +469,1521 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vínculos empregatícios ativos em 31/12. Fonte: RAIS/MTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Seção</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Nome Seção</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2001</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2003</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2005</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2007</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2009</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2011</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2013</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2015</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2017</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2019</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2021</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2023</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Emp. 2025</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2001</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2003</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2005</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2007</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2009</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2011</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2013</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2015</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2017</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2019</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2021</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2023</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>QL 2025</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>QL Médio</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>Representat. (%)</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>Cresc. 5 anos (%)</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Consistência (0-12)</t>
+          <t>Vínculos empregatícios ativos em 31/12. QL calculado no nível de Seção. Fonte: RAIS/MTE.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>130</v>
-      </c>
-      <c r="D4" t="n">
-        <v>614</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1357</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1869</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1486</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1451</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1175</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1122</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1059</v>
-      </c>
-      <c r="L4" t="n">
-        <v>865</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1074</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1269</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1384</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.722794</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.564606</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5.545034</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7.146759</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6.763353</v>
-      </c>
-      <c r="U4" t="n">
-        <v>6.165937</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.6714</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.623081</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.350718</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5.616054</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.595214</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.663382</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.986851</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.262706</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22.412955</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>6/12</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Seção</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Nome Seção</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2001</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2003</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2005</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2007</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2009</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2011</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2013</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2015</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2017</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2019</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2021</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2023</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Emp. 2025</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2001</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2003</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2005</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2007</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2009</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2011</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2013</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2015</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2017</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2019</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2021</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2023</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>QL 2025</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>QL Médio</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>Representat. (%)</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>Cresc. 5 anos (%)</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Consistência (0-12)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>614</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1357</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>1869</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>1486</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1451</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1175</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1074</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1269</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.722794</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.579977</v>
+        <v>3.564606</v>
       </c>
       <c r="R5" t="n">
-        <v>0.117362</v>
+        <v>5.545034</v>
       </c>
       <c r="S5" t="n">
-        <v>0.133891</v>
+        <v>7.146759</v>
       </c>
       <c r="T5" t="n">
-        <v>0.016395</v>
+        <v>6.763353</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>6.165937</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.6714</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.623081</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.350718</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>5.616054</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.595214</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.663382</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>6.986851</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.065202</v>
+        <v>5.262706</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>22.412955</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>60</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1214</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1216</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>1745</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>774</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>590</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>482</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>453</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>463</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.451395</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.418721</v>
+        <v>0.579977</v>
       </c>
       <c r="R6" t="n">
-        <v>2.621063</v>
+        <v>0.117362</v>
       </c>
       <c r="S6" t="n">
-        <v>1.898934</v>
+        <v>0.133891</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69953</v>
+        <v>0.016395</v>
       </c>
       <c r="U6" t="n">
-        <v>1.881534</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.619561</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.484576</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.242998</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24366</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.09549</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.906699</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.864035</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.802169</v>
+        <v>0.065202</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.271255</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.883002</v>
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELETRICIDADE E GÁS</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1216</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1745</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>774</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>590</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>605</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>534</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>482</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>449</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.451395</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.28434</v>
+        <v>2.418721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.205871</v>
+        <v>2.621063</v>
       </c>
       <c r="S7" t="n">
-        <v>0.120332</v>
+        <v>1.898934</v>
       </c>
       <c r="T7" t="n">
-        <v>0.163207</v>
+        <v>1.69953</v>
       </c>
       <c r="U7" t="n">
-        <v>0.23634</v>
+        <v>1.881534</v>
       </c>
       <c r="V7" t="n">
-        <v>0.07205300000000001</v>
+        <v>1.619561</v>
       </c>
       <c r="W7" t="n">
-        <v>0.071616</v>
+        <v>1.484576</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.242998</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24366</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.09549</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.906699</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.188135</v>
+        <v>0.864035</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.103223</v>
+        <v>1.802169</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.064777</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7.271255</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.883002</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
+          <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0.933705</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.455393</v>
+        <v>0.28434</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616139</v>
+        <v>0.205871</v>
       </c>
       <c r="S8" t="n">
-        <v>0.350211</v>
+        <v>0.120332</v>
       </c>
       <c r="T8" t="n">
-        <v>1.608887</v>
+        <v>0.163207</v>
       </c>
       <c r="U8" t="n">
-        <v>2.018467</v>
+        <v>0.23634</v>
       </c>
       <c r="V8" t="n">
-        <v>2.222094</v>
+        <v>0.07205300000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>4.075202</v>
+        <v>0.071616</v>
       </c>
       <c r="X8" t="n">
-        <v>2.354762</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.708731</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.950902</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.467984</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.370414</v>
+        <v>0.188135</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.471761</v>
+        <v>0.103223</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.226721</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-66.666667</v>
+        <v>0.064777</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO</t>
+          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H9" t="n">
+        <v>43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>56</v>
+      </c>
+      <c r="J9" t="n">
+        <v>102</v>
+      </c>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="n">
         <v>42</v>
       </c>
-      <c r="I9" t="n">
-        <v>36</v>
-      </c>
-      <c r="J9" t="n">
-        <v>78</v>
-      </c>
-      <c r="K9" t="n">
-        <v>120</v>
-      </c>
-      <c r="L9" t="n">
-        <v>38</v>
-      </c>
       <c r="M9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N9" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007472</v>
+        <v>0.933705</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.025398</v>
+        <v>0.455393</v>
       </c>
       <c r="R9" t="n">
-        <v>0.020965</v>
+        <v>0.616139</v>
       </c>
       <c r="S9" t="n">
-        <v>0.026872</v>
+        <v>0.350211</v>
       </c>
       <c r="T9" t="n">
-        <v>0.119443</v>
+        <v>1.608887</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11055</v>
+        <v>2.018467</v>
       </c>
       <c r="V9" t="n">
-        <v>0.070206</v>
+        <v>2.222094</v>
       </c>
       <c r="W9" t="n">
-        <v>0.186069</v>
+        <v>4.075202</v>
       </c>
       <c r="X9" t="n">
-        <v>0.436213</v>
+        <v>2.354762</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.216171</v>
+        <v>1.708731</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.241419</v>
+        <v>1.950902</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.245087</v>
+        <v>0.467984</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.29027</v>
+        <v>0.370414</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.153549</v>
+        <v>1.471761</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.311741</v>
+        <v>0.226721</v>
       </c>
       <c r="AE9" t="n">
-        <v>113.157895</v>
+        <v>-66.666667</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>393</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>555</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>581</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>648</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>857</v>
+        <v>42</v>
       </c>
       <c r="I10" t="n">
-        <v>1243</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>1229</v>
+        <v>78</v>
       </c>
       <c r="K10" t="n">
-        <v>1222</v>
+        <v>120</v>
       </c>
       <c r="L10" t="n">
-        <v>1150</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>1500</v>
+        <v>59</v>
       </c>
       <c r="N10" t="n">
-        <v>1529</v>
+        <v>73</v>
       </c>
       <c r="O10" t="n">
-        <v>1595</v>
+        <v>81</v>
       </c>
       <c r="P10" t="n">
-        <v>0.852403</v>
+        <v>0.007472</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.590398</v>
+        <v>0.025398</v>
       </c>
       <c r="R10" t="n">
-        <v>0.602399</v>
+        <v>0.020965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.666035</v>
+        <v>0.026872</v>
       </c>
       <c r="T10" t="n">
-        <v>0.778231</v>
+        <v>0.119443</v>
       </c>
       <c r="U10" t="n">
-        <v>0.985965</v>
+        <v>0.11055</v>
       </c>
       <c r="V10" t="n">
-        <v>1.275208</v>
+        <v>0.070206</v>
       </c>
       <c r="W10" t="n">
-        <v>1.269721</v>
+        <v>0.186069</v>
       </c>
       <c r="X10" t="n">
-        <v>1.335069</v>
+        <v>0.436213</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.439309</v>
+        <v>0.216171</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.506635</v>
+        <v>0.241419</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.434158</v>
+        <v>0.245087</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.527343</v>
+        <v>0.29027</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.097144</v>
+        <v>0.153549</v>
       </c>
       <c r="AD10" t="n">
-        <v>25.82996</v>
+        <v>1.311741</v>
       </c>
       <c r="AE10" t="n">
-        <v>38.695652</v>
+        <v>113.157895</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>10/12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>310</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>393</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>555</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>581</v>
       </c>
       <c r="G11" t="n">
-        <v>41</v>
+        <v>648</v>
       </c>
       <c r="H11" t="n">
-        <v>48</v>
+        <v>857</v>
       </c>
       <c r="I11" t="n">
-        <v>61</v>
+        <v>1243</v>
       </c>
       <c r="J11" t="n">
-        <v>48</v>
+        <v>1229</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>1222</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>1150</v>
       </c>
       <c r="M11" t="n">
-        <v>84</v>
+        <v>1500</v>
       </c>
       <c r="N11" t="n">
-        <v>179</v>
+        <v>1529</v>
       </c>
       <c r="O11" t="n">
-        <v>251</v>
+        <v>1595</v>
       </c>
       <c r="P11" t="n">
-        <v>0.223095</v>
+        <v>0.852403</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.121616</v>
+        <v>0.590398</v>
       </c>
       <c r="R11" t="n">
-        <v>0.187086</v>
+        <v>0.602399</v>
       </c>
       <c r="S11" t="n">
-        <v>0.174979</v>
+        <v>0.666035</v>
       </c>
       <c r="T11" t="n">
-        <v>0.232269</v>
+        <v>0.778231</v>
       </c>
       <c r="U11" t="n">
-        <v>0.257261</v>
+        <v>0.985965</v>
       </c>
       <c r="V11" t="n">
-        <v>0.313604</v>
+        <v>1.275208</v>
       </c>
       <c r="W11" t="n">
-        <v>0.236245</v>
+        <v>1.269721</v>
       </c>
       <c r="X11" t="n">
-        <v>0.185893</v>
+        <v>1.335069</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.330419</v>
+        <v>1.439309</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.415544</v>
+        <v>1.506635</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.798519</v>
+        <v>1.434158</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.124877</v>
+        <v>1.527343</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.353954</v>
+        <v>1.097144</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.064777</v>
+        <v>25.82996</v>
       </c>
       <c r="AE11" t="n">
-        <v>356.363636</v>
+        <v>38.695652</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H12" t="n">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J12" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="K12" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="N12" t="n">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="O12" t="n">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.223095</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.051069</v>
+        <v>0.121616</v>
       </c>
       <c r="R12" t="n">
-        <v>0.110719</v>
+        <v>0.187086</v>
       </c>
       <c r="S12" t="n">
-        <v>0.334889</v>
+        <v>0.174979</v>
       </c>
       <c r="T12" t="n">
-        <v>0.281534</v>
+        <v>0.232269</v>
       </c>
       <c r="U12" t="n">
-        <v>0.966625</v>
+        <v>0.257261</v>
       </c>
       <c r="V12" t="n">
-        <v>0.663236</v>
+        <v>0.313604</v>
       </c>
       <c r="W12" t="n">
-        <v>0.70512</v>
+        <v>0.236245</v>
       </c>
       <c r="X12" t="n">
-        <v>0.789041</v>
+        <v>0.185893</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.824359</v>
+        <v>0.330419</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5392130000000001</v>
+        <v>0.415544</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.636854</v>
+        <v>0.798519</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.486328</v>
+        <v>1.124877</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.491461</v>
+        <v>0.353954</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.311741</v>
+        <v>4.064777</v>
       </c>
       <c r="AE12" t="n">
-        <v>-10</v>
+        <v>356.363636</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="N13" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.139804</v>
+        <v>0.051069</v>
       </c>
       <c r="R13" t="n">
-        <v>0.021692</v>
+        <v>0.110719</v>
       </c>
       <c r="S13" t="n">
-        <v>0.028182</v>
+        <v>0.334889</v>
       </c>
       <c r="T13" t="n">
-        <v>0.144878</v>
+        <v>0.281534</v>
       </c>
       <c r="U13" t="n">
-        <v>0.267953</v>
+        <v>0.966625</v>
       </c>
       <c r="V13" t="n">
-        <v>0.148759</v>
+        <v>0.663236</v>
       </c>
       <c r="W13" t="n">
-        <v>0.229764</v>
+        <v>0.70512</v>
       </c>
       <c r="X13" t="n">
-        <v>0.302121</v>
+        <v>0.789041</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.623492</v>
+        <v>0.824359</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.635722</v>
+        <v>0.5392130000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.393436</v>
+        <v>0.636854</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.42958</v>
+        <v>0.486328</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.258876</v>
+        <v>0.491461</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.453441</v>
+        <v>1.311741</v>
       </c>
       <c r="AE13" t="n">
-        <v>7.692308</v>
+        <v>-10</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
-        <v>21</v>
-      </c>
-      <c r="F14" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" t="n">
-        <v>29</v>
-      </c>
-      <c r="H14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" t="n">
-        <v>42</v>
-      </c>
-      <c r="J14" t="n">
-        <v>61</v>
-      </c>
-      <c r="K14" t="n">
-        <v>65</v>
-      </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="N14" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="O14" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>0.38214</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.260456</v>
+        <v>0.139804</v>
       </c>
       <c r="R14" t="n">
-        <v>0.313984</v>
+        <v>0.021692</v>
       </c>
       <c r="S14" t="n">
-        <v>0.251112</v>
+        <v>0.028182</v>
       </c>
       <c r="T14" t="n">
-        <v>0.480168</v>
+        <v>0.144878</v>
       </c>
       <c r="U14" t="n">
-        <v>0.728461</v>
+        <v>0.267953</v>
       </c>
       <c r="V14" t="n">
-        <v>0.716247</v>
+        <v>0.148759</v>
       </c>
       <c r="W14" t="n">
-        <v>1.010231</v>
+        <v>0.229764</v>
       </c>
       <c r="X14" t="n">
-        <v>1.065241</v>
+        <v>0.302121</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.113347</v>
+        <v>0.623492</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.199699</v>
+        <v>0.635722</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.212402</v>
+        <v>0.393436</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.336888</v>
+        <v>0.42958</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.774644</v>
+        <v>0.258876</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.311741</v>
+        <v>0.453441</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>7.692308</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="M15" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.38214</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.260456</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.313984</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.251112</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.480168</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.728461</v>
       </c>
       <c r="V15" t="n">
-        <v>0.165509</v>
+        <v>0.716247</v>
       </c>
       <c r="W15" t="n">
-        <v>0.411244</v>
+        <v>1.010231</v>
       </c>
       <c r="X15" t="n">
-        <v>0.199752</v>
+        <v>1.065241</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.474655</v>
+        <v>1.113347</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.197421</v>
+        <v>1.199699</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.7092540000000001</v>
+        <v>1.212402</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.66889</v>
+        <v>1.336888</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.294363</v>
+        <v>0.774644</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.129555</v>
+        <v>1.311741</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N16" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="n">
-        <v>23</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" t="n">
-        <v>31</v>
-      </c>
-      <c r="I16" t="n">
-        <v>38</v>
-      </c>
-      <c r="J16" t="n">
-        <v>56</v>
-      </c>
-      <c r="K16" t="n">
-        <v>52</v>
-      </c>
-      <c r="L16" t="n">
-        <v>43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>58</v>
-      </c>
-      <c r="N16" t="n">
-        <v>87</v>
-      </c>
       <c r="O16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.165509</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.411244</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.199752</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.474655</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.197421</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.7092540000000001</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.66889</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.294363</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.129555</v>
+      </c>
+      <c r="AE16" t="n">
         <v>100</v>
       </c>
-      <c r="P16" t="n">
-        <v>0.394203</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.238539</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.413326</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.342774</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.306467</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.449513</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.500656</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.772019</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.6937720000000001</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.607801</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.59253</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.672283</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.760549</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.518803</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.619433</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>132.55814</v>
-      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>535</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J17" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="K17" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="N17" t="n">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="O17" t="n">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>0.036792</v>
+        <v>0.394203</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.420087</v>
+        <v>0.238539</v>
       </c>
       <c r="R17" t="n">
-        <v>0.108442</v>
+        <v>0.413326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.134528</v>
+        <v>0.342774</v>
       </c>
       <c r="T17" t="n">
-        <v>0.056833</v>
+        <v>0.306467</v>
       </c>
       <c r="U17" t="n">
-        <v>0.033541</v>
+        <v>0.449513</v>
       </c>
       <c r="V17" t="n">
-        <v>0.059562</v>
+        <v>0.500656</v>
       </c>
       <c r="W17" t="n">
-        <v>0.08073900000000001</v>
+        <v>0.772019</v>
       </c>
       <c r="X17" t="n">
-        <v>0.122994</v>
+        <v>0.6937720000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.051558</v>
+        <v>0.607801</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.317911</v>
+        <v>0.59253</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.397376</v>
+        <v>0.672283</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.292626</v>
+        <v>0.760549</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.316384</v>
+        <v>0.518803</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.380567</v>
+        <v>1.619433</v>
       </c>
       <c r="AE17" t="n">
-        <v>880</v>
+        <v>132.55814</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2098,626 +1994,730 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>483</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1122</v>
+        <v>535</v>
       </c>
       <c r="E18" t="n">
-        <v>1362</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>1159</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>1594</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>1481</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>1834</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>1658</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>1594</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>1299</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>1373</v>
+        <v>119</v>
       </c>
       <c r="N18" t="n">
-        <v>1786</v>
+        <v>188</v>
       </c>
       <c r="O18" t="n">
-        <v>1759</v>
+        <v>147</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5784049999999999</v>
+        <v>0.036792</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.740063</v>
+        <v>2.420087</v>
       </c>
       <c r="R18" t="n">
-        <v>0.707754</v>
+        <v>0.108442</v>
       </c>
       <c r="S18" t="n">
-        <v>0.732387</v>
+        <v>0.134528</v>
       </c>
       <c r="T18" t="n">
-        <v>0.89181</v>
+        <v>0.056833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.834413</v>
+        <v>0.033541</v>
       </c>
       <c r="V18" t="n">
-        <v>1.034553</v>
+        <v>0.059562</v>
       </c>
       <c r="W18" t="n">
-        <v>0.97373</v>
+        <v>0.08073900000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>0.941526</v>
+        <v>0.122994</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8478560000000001</v>
+        <v>0.051558</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.784398</v>
+        <v>0.317911</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.957722</v>
+        <v>0.397376</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.830109</v>
+        <v>0.292626</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.834979</v>
+        <v>0.316384</v>
       </c>
       <c r="AD18" t="n">
-        <v>28.48583</v>
+        <v>2.380567</v>
       </c>
       <c r="AE18" t="n">
-        <v>35.411855</v>
+        <v>880</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>1122</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>1362</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>1159</v>
       </c>
       <c r="G19" t="n">
-        <v>32</v>
+        <v>1594</v>
       </c>
       <c r="H19" t="n">
-        <v>51</v>
+        <v>1481</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>1834</v>
       </c>
       <c r="J19" t="n">
-        <v>36</v>
+        <v>1658</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>1594</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>1299</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>1373</v>
       </c>
       <c r="N19" t="n">
-        <v>89</v>
+        <v>1786</v>
       </c>
       <c r="O19" t="n">
-        <v>107</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1759</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5784049999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.145671</v>
+        <v>0.740063</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1786</v>
+        <v>0.707754</v>
       </c>
       <c r="S19" t="n">
-        <v>0.266092</v>
+        <v>0.732387</v>
       </c>
       <c r="T19" t="n">
-        <v>0.281206</v>
+        <v>0.89181</v>
       </c>
       <c r="U19" t="n">
-        <v>0.375087</v>
+        <v>0.834413</v>
       </c>
       <c r="V19" t="n">
-        <v>0.079683</v>
+        <v>1.034553</v>
       </c>
       <c r="W19" t="n">
-        <v>0.190439</v>
+        <v>0.97373</v>
       </c>
       <c r="X19" t="n">
-        <v>0.165394</v>
+        <v>0.941526</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.227931</v>
+        <v>0.8478560000000001</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.290763</v>
+        <v>0.784398</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.226945</v>
+        <v>0.957722</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.307651</v>
+        <v>0.830109</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.227955</v>
+        <v>0.834979</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.732794</v>
+        <v>28.48583</v>
       </c>
       <c r="AE19" t="n">
-        <v>167.5</v>
+        <v>35.411855</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38</v>
+      </c>
+      <c r="G20" t="n">
         <v>32</v>
       </c>
-      <c r="F20" t="n">
-        <v>23</v>
-      </c>
-      <c r="G20" t="n">
-        <v>25</v>
-      </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L20" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="M20" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="O20" t="n">
-        <v>48</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.293025</v>
+        <v>107</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>0.235668</v>
+        <v>0.145671</v>
       </c>
       <c r="R20" t="n">
-        <v>0.237382</v>
+        <v>0.1786</v>
       </c>
       <c r="S20" t="n">
-        <v>0.188163</v>
+        <v>0.266092</v>
       </c>
       <c r="T20" t="n">
-        <v>0.207054</v>
+        <v>0.281206</v>
       </c>
       <c r="U20" t="n">
-        <v>0.137152</v>
+        <v>0.375087</v>
       </c>
       <c r="V20" t="n">
-        <v>0.198991</v>
+        <v>0.079683</v>
       </c>
       <c r="W20" t="n">
-        <v>0.188282</v>
+        <v>0.190439</v>
       </c>
       <c r="X20" t="n">
-        <v>0.067439</v>
+        <v>0.165394</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.419379</v>
+        <v>0.227931</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.211736</v>
+        <v>0.290763</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.205824</v>
+        <v>0.226945</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.180416</v>
+        <v>0.307651</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.213116</v>
+        <v>0.227955</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.777328</v>
+        <v>1.732794</v>
       </c>
       <c r="AE20" t="n">
-        <v>-22.580645</v>
+        <v>167.5</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
+          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="P21" t="n">
-        <v>0.159068</v>
+        <v>0.293025</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.054362</v>
+        <v>0.235668</v>
       </c>
       <c r="R21" t="n">
-        <v>0.192546</v>
+        <v>0.237382</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.188163</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.207054</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.137152</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.198991</v>
       </c>
       <c r="W21" t="n">
-        <v>0.293507</v>
+        <v>0.188282</v>
       </c>
       <c r="X21" t="n">
-        <v>0.434757</v>
+        <v>0.067439</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.413615</v>
+        <v>0.419379</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.700404</v>
+        <v>0.211736</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.676406</v>
+        <v>0.205824</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.579134</v>
+        <v>0.180416</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.269523</v>
+        <v>0.213116</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.259109</v>
+        <v>0.777328</v>
       </c>
       <c r="AE21" t="n">
-        <v>166.666667</v>
+        <v>-22.580645</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="n">
-        <v>12</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
         <v>11</v>
       </c>
-      <c r="H22" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="N22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>21</v>
-      </c>
-      <c r="K22" t="n">
-        <v>69</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13</v>
-      </c>
-      <c r="M22" t="n">
-        <v>17</v>
-      </c>
-      <c r="N22" t="n">
-        <v>17</v>
-      </c>
       <c r="O22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>0.041181</v>
+        <v>0.159068</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.08431</v>
+        <v>0.054362</v>
       </c>
       <c r="R22" t="n">
-        <v>0.08167099999999999</v>
+        <v>0.192546</v>
       </c>
       <c r="S22" t="n">
-        <v>0.117956</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.126227</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.203195</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.190978</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.235758</v>
+        <v>0.293507</v>
       </c>
       <c r="X22" t="n">
-        <v>0.823396</v>
+        <v>0.434757</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.190031</v>
+        <v>0.413615</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.215191</v>
+        <v>0.700404</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.165231</v>
+        <v>0.676406</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.225912</v>
+        <v>0.579134</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.207772</v>
+        <v>0.269523</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.356275</v>
+        <v>0.259109</v>
       </c>
       <c r="AE22" t="n">
-        <v>69.230769</v>
+        <v>166.666667</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17</v>
+      </c>
+      <c r="I23" t="n">
+        <v>16</v>
+      </c>
+      <c r="J23" t="n">
+        <v>21</v>
+      </c>
+      <c r="K23" t="n">
+        <v>69</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13</v>
+      </c>
+      <c r="M23" t="n">
+        <v>17</v>
+      </c>
+      <c r="N23" t="n">
+        <v>17</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.041181</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.08431</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.08167099999999999</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.117956</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.126227</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.203195</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.190978</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.235758</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.823396</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.190031</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.215191</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.165231</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.225912</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.207772</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.356275</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>69.230769</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>7/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.805986</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
         <v>0.061999</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>

--- a/Empregos_por_Secao_CNAE_RAIS_Capanema.xlsx
+++ b/Empregos_por_Secao_CNAE_RAIS_Capanema.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,47 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A5E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2A5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,10 +87,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,2305 +468,2310 @@
   <dimension ref="A1:AF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>EMPREGOS POR SEÇÃO CNAE (RAIS) — CAPANEMA vs PARÁ — SÉRIE 2001-2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos empregatícios ativos em 31/12. QL calculado no nível de Seção. Fonte: RAIS/MTE.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Nome Seção</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2001</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2003</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2005</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2007</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2009</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2011</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2013</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2015</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2017</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2019</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2021</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2023</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Emp. 2025</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>QL 2001</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>QL 2003</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>QL 2005</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>QL 2007</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>QL 2009</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>QL 2011</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>QL 2013</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>QL 2015</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>QL 2017</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>QL 2019</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>QL 2021</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>QL 2023</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>QL 2025</t>
         </is>
       </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>QL Médio</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>Representat. (%)</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>Cresc. 5 anos (%)</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="inlineStr">
+      <c r="AF4" s="5" t="inlineStr">
         <is>
           <t>Consistência (0-12)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>614</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="7" t="n">
         <v>1357</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>1869</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="7" t="n">
         <v>1486</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="7" t="n">
         <v>1451</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="7" t="n">
         <v>1122</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="7" t="n">
         <v>1059</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="7" t="n">
         <v>865</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="7" t="n">
         <v>1074</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="7" t="n">
         <v>1269</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="7" t="n">
         <v>1384</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="7" t="n">
         <v>1.722794</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="7" t="n">
         <v>3.564606</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="7" t="n">
         <v>5.545034</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="7" t="n">
         <v>7.146759</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="7" t="n">
         <v>6.763353</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="7" t="n">
         <v>6.165937</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="7" t="n">
         <v>4.6714</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5" s="7" t="n">
         <v>4.623081</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5" s="7" t="n">
         <v>4.350718</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5" s="7" t="n">
         <v>5.616054</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5" s="7" t="n">
         <v>5.595214</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="7" t="n">
         <v>5.663382</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB5" s="7" t="n">
         <v>6.986851</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5" s="7" t="n">
         <v>5.262706</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD5" s="7" t="n">
         <v>22.412955</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE5" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF5" s="7" t="inlineStr">
         <is>
           <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="H6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>0.579977</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="9" t="n">
         <v>0.117362</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="9" t="n">
         <v>0.133891</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" s="9" t="n">
         <v>0.016395</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="U6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9" t="n">
         <v>0.065202</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF6" s="9" t="inlineStr">
         <is>
           <t>2/12</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="7" t="n">
         <v>1214</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>1216</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>1745</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>774</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="7" t="n">
         <v>605</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="7" t="n">
         <v>534</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="7" t="n">
         <v>482</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="7" t="n">
         <v>395</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="7" t="n">
         <v>453</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="7" t="n">
         <v>512</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="7" t="n">
         <v>463</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="7" t="n">
         <v>449</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="7" t="n">
         <v>4.451395</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="7" t="n">
         <v>2.418721</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="7" t="n">
         <v>2.621063</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="7" t="n">
         <v>1.898934</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="7" t="n">
         <v>1.69953</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="7" t="n">
         <v>1.881534</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="7" t="n">
         <v>1.619561</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7" s="7" t="n">
         <v>1.484576</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7" s="7" t="n">
         <v>1.242998</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7" s="7" t="n">
         <v>1.24366</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7" s="7" t="n">
         <v>1.09549</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="7" t="n">
         <v>0.906699</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB7" s="7" t="n">
         <v>0.864035</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7" s="7" t="n">
         <v>1.802169</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD7" s="7" t="n">
         <v>7.271255</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE7" s="7" t="n">
         <v>-0.883002</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF7" s="7" t="inlineStr">
         <is>
           <t>5/12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="K8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="P8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9" t="n">
         <v>0.28434</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="9" t="n">
         <v>0.205871</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="9" t="n">
         <v>0.120332</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="9" t="n">
         <v>0.163207</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8" s="9" t="n">
         <v>0.23634</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" s="9" t="n">
         <v>0.07205300000000001</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W8" s="9" t="n">
         <v>0.071616</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9" t="n">
         <v>0.188135</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC8" s="9" t="n">
         <v>0.103223</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD8" s="9" t="n">
         <v>0.064777</v>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8" s="9" t="inlineStr">
         <is>
           <t>3/12</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="7" t="n">
         <v>0.933705</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="7" t="n">
         <v>0.455393</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="7" t="n">
         <v>0.616139</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="7" t="n">
         <v>0.350211</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="7" t="n">
         <v>1.608887</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9" s="7" t="n">
         <v>2.018467</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="7" t="n">
         <v>2.222094</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W9" s="7" t="n">
         <v>4.075202</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9" s="7" t="n">
         <v>2.354762</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9" s="7" t="n">
         <v>1.708731</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9" s="7" t="n">
         <v>1.950902</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="7" t="n">
         <v>0.467984</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB9" s="7" t="n">
         <v>0.370414</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9" s="7" t="n">
         <v>1.471761</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9" s="7" t="n">
         <v>0.226721</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9" s="7" t="n">
         <v>-66.666667</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF9" s="7" t="inlineStr">
         <is>
           <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="9" t="n">
         <v>0.007472</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="9" t="n">
         <v>0.025398</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="9" t="n">
         <v>0.020965</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="9" t="n">
         <v>0.026872</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="9" t="n">
         <v>0.119443</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.11055</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="9" t="n">
         <v>0.070206</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10" s="9" t="n">
         <v>0.186069</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10" s="9" t="n">
         <v>0.436213</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10" s="9" t="n">
         <v>0.216171</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10" s="9" t="n">
         <v>0.241419</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="9" t="n">
         <v>0.245087</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB10" s="9" t="n">
         <v>0.29027</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10" s="9" t="n">
         <v>0.153549</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10" s="9" t="n">
         <v>1.311741</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10" s="9" t="n">
         <v>113.157895</v>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF10" s="9" t="inlineStr">
         <is>
           <t>10/12</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="7" t="n">
         <v>310</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>393</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="7" t="n">
         <v>555</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>581</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>648</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>857</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>1243</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="7" t="n">
         <v>1229</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="7" t="n">
         <v>1222</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="7" t="n">
         <v>1150</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="7" t="n">
         <v>1500</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="7" t="n">
         <v>1529</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="7" t="n">
         <v>1595</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="7" t="n">
         <v>0.852403</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="7" t="n">
         <v>0.590398</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="7" t="n">
         <v>0.602399</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="7" t="n">
         <v>0.666035</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="7" t="n">
         <v>0.778231</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11" s="7" t="n">
         <v>0.985965</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" s="7" t="n">
         <v>1.275208</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W11" s="7" t="n">
         <v>1.269721</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X11" s="7" t="n">
         <v>1.335069</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11" s="7" t="n">
         <v>1.439309</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11" s="7" t="n">
         <v>1.506635</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="7" t="n">
         <v>1.434158</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB11" s="7" t="n">
         <v>1.527343</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC11" s="7" t="n">
         <v>1.097144</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD11" s="7" t="n">
         <v>25.82996</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11" s="7" t="n">
         <v>38.695652</v>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF11" s="7" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="9" t="n">
         <v>179</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="9" t="n">
         <v>0.223095</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="9" t="n">
         <v>0.121616</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="9" t="n">
         <v>0.187086</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="9" t="n">
         <v>0.174979</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" s="9" t="n">
         <v>0.232269</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12" s="9" t="n">
         <v>0.257261</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12" s="9" t="n">
         <v>0.313604</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W12" s="9" t="n">
         <v>0.236245</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12" s="9" t="n">
         <v>0.185893</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12" s="9" t="n">
         <v>0.330419</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12" s="9" t="n">
         <v>0.415544</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="9" t="n">
         <v>0.798519</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB12" s="9" t="n">
         <v>1.124877</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC12" s="9" t="n">
         <v>0.353954</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD12" s="9" t="n">
         <v>4.064777</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE12" s="9" t="n">
         <v>356.363636</v>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF12" s="9" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7" t="n">
         <v>0.051069</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="7" t="n">
         <v>0.110719</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="7" t="n">
         <v>0.334889</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" s="7" t="n">
         <v>0.281534</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13" s="7" t="n">
         <v>0.966625</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13" s="7" t="n">
         <v>0.663236</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W13" s="7" t="n">
         <v>0.70512</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X13" s="7" t="n">
         <v>0.789041</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13" s="7" t="n">
         <v>0.824359</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z13" s="7" t="n">
         <v>0.5392130000000001</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="7" t="n">
         <v>0.636854</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AB13" s="7" t="n">
         <v>0.486328</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC13" s="7" t="n">
         <v>0.491461</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD13" s="7" t="n">
         <v>1.311741</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE13" s="7" t="n">
         <v>-10</v>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="P14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="n">
         <v>0.139804</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="9" t="n">
         <v>0.021692</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="9" t="n">
         <v>0.028182</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="9" t="n">
         <v>0.144878</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14" s="9" t="n">
         <v>0.267953</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14" s="9" t="n">
         <v>0.148759</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W14" s="9" t="n">
         <v>0.229764</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X14" s="9" t="n">
         <v>0.302121</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14" s="9" t="n">
         <v>0.623492</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z14" s="9" t="n">
         <v>0.635722</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="9" t="n">
         <v>0.393436</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB14" s="9" t="n">
         <v>0.42958</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14" s="9" t="n">
         <v>0.258876</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD14" s="9" t="n">
         <v>0.453441</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE14" s="9" t="n">
         <v>7.692308</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF14" s="9" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="7" t="n">
         <v>0.38214</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="7" t="n">
         <v>0.260456</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="7" t="n">
         <v>0.313984</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="7" t="n">
         <v>0.251112</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="7" t="n">
         <v>0.480168</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15" s="7" t="n">
         <v>0.728461</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15" s="7" t="n">
         <v>0.716247</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W15" s="7" t="n">
         <v>1.010231</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X15" s="7" t="n">
         <v>1.065241</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15" s="7" t="n">
         <v>1.113347</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z15" s="7" t="n">
         <v>1.199699</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="7" t="n">
         <v>1.212402</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB15" s="7" t="n">
         <v>1.336888</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC15" s="7" t="n">
         <v>0.774644</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD15" s="7" t="n">
         <v>1.311741</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE15" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="C16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="P16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>0.165509</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W16" s="9" t="n">
         <v>0.411244</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X16" s="9" t="n">
         <v>0.199752</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16" s="9" t="n">
         <v>0.474655</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z16" s="9" t="n">
         <v>1.197421</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="9" t="n">
         <v>0.7092540000000001</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB16" s="9" t="n">
         <v>0.66889</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC16" s="9" t="n">
         <v>0.294363</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD16" s="9" t="n">
         <v>0.129555</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE16" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF16" s="9" t="inlineStr">
         <is>
           <t>4/12</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="7" t="n">
         <v>0.394203</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="7" t="n">
         <v>0.238539</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="7" t="n">
         <v>0.413326</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="7" t="n">
         <v>0.342774</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="7" t="n">
         <v>0.306467</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17" s="7" t="n">
         <v>0.449513</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17" s="7" t="n">
         <v>0.500656</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W17" s="7" t="n">
         <v>0.772019</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X17" s="7" t="n">
         <v>0.6937720000000001</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17" s="7" t="n">
         <v>0.607801</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z17" s="7" t="n">
         <v>0.59253</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="7" t="n">
         <v>0.672283</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB17" s="7" t="n">
         <v>0.760549</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC17" s="7" t="n">
         <v>0.518803</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD17" s="7" t="n">
         <v>1.619433</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE17" s="7" t="n">
         <v>132.55814</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="9" t="n">
         <v>535</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="9" t="n">
         <v>188</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="9" t="n">
         <v>147</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="9" t="n">
         <v>0.036792</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="9" t="n">
         <v>2.420087</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="9" t="n">
         <v>0.108442</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="9" t="n">
         <v>0.134528</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" s="9" t="n">
         <v>0.056833</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.033541</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18" s="9" t="n">
         <v>0.059562</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W18" s="9" t="n">
         <v>0.08073900000000001</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X18" s="9" t="n">
         <v>0.122994</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18" s="9" t="n">
         <v>0.051558</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18" s="9" t="n">
         <v>0.317911</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="9" t="n">
         <v>0.397376</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB18" s="9" t="n">
         <v>0.292626</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC18" s="9" t="n">
         <v>0.316384</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD18" s="9" t="n">
         <v>2.380567</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE18" s="9" t="n">
         <v>880</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF18" s="9" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="7" t="n">
         <v>483</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="7" t="n">
         <v>1122</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="7" t="n">
         <v>1362</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="7" t="n">
         <v>1159</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="7" t="n">
         <v>1594</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="7" t="n">
         <v>1481</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="7" t="n">
         <v>1834</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="7" t="n">
         <v>1658</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="7" t="n">
         <v>1594</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="7" t="n">
         <v>1373</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="7" t="n">
         <v>1786</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="7" t="n">
         <v>1759</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="7" t="n">
         <v>0.5784049999999999</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="7" t="n">
         <v>0.740063</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19" s="7" t="n">
         <v>0.707754</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="7" t="n">
         <v>0.732387</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" s="7" t="n">
         <v>0.89181</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U19" s="7" t="n">
         <v>0.834413</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19" s="7" t="n">
         <v>1.034553</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W19" s="7" t="n">
         <v>0.97373</v>
       </c>
-      <c r="X19" t="n">
+      <c r="X19" s="7" t="n">
         <v>0.941526</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19" s="7" t="n">
         <v>0.8478560000000001</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z19" s="7" t="n">
         <v>0.784398</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="7" t="n">
         <v>0.957722</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AB19" s="7" t="n">
         <v>0.830109</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AC19" s="7" t="n">
         <v>0.834979</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD19" s="7" t="n">
         <v>28.48583</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AE19" s="7" t="n">
         <v>35.411855</v>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF19" s="7" t="inlineStr">
         <is>
           <t>6/12</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="9" t="n">
         <v>107</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="9" t="n">
         <v>0.145671</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" s="9" t="n">
         <v>0.1786</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="9" t="n">
         <v>0.266092</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" s="9" t="n">
         <v>0.281206</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U20" s="9" t="n">
         <v>0.375087</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20" s="9" t="n">
         <v>0.079683</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W20" s="9" t="n">
         <v>0.190439</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X20" s="9" t="n">
         <v>0.165394</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20" s="9" t="n">
         <v>0.227931</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z20" s="9" t="n">
         <v>0.290763</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="9" t="n">
         <v>0.226945</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AB20" s="9" t="n">
         <v>0.307651</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC20" s="9" t="n">
         <v>0.227955</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AD20" s="9" t="n">
         <v>1.732794</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE20" s="9" t="n">
         <v>167.5</v>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AF20" s="9" t="inlineStr">
         <is>
           <t>9/12</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="7" t="n">
         <v>0.293025</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="7" t="n">
         <v>0.235668</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" s="7" t="n">
         <v>0.237382</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="7" t="n">
         <v>0.188163</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" s="7" t="n">
         <v>0.207054</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U21" s="7" t="n">
         <v>0.137152</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V21" s="7" t="n">
         <v>0.198991</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W21" s="7" t="n">
         <v>0.188282</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X21" s="7" t="n">
         <v>0.067439</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21" s="7" t="n">
         <v>0.419379</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z21" s="7" t="n">
         <v>0.211736</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA21" s="7" t="n">
         <v>0.205824</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AB21" s="7" t="n">
         <v>0.180416</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC21" s="7" t="n">
         <v>0.213116</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AD21" s="7" t="n">
         <v>0.777328</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AE21" s="7" t="n">
         <v>-22.580645</v>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AF21" s="7" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="F22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="9" t="n">
         <v>0.159068</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="9" t="n">
         <v>0.054362</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="9" t="n">
         <v>0.192546</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="S22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="9" t="n">
         <v>0.293507</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X22" s="9" t="n">
         <v>0.434757</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22" s="9" t="n">
         <v>0.413615</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z22" s="9" t="n">
         <v>0.700404</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA22" s="9" t="n">
         <v>0.676406</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AB22" s="9" t="n">
         <v>0.579134</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AC22" s="9" t="n">
         <v>0.269523</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AD22" s="9" t="n">
         <v>0.259109</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE22" s="9" t="n">
         <v>166.666667</v>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AF22" s="9" t="inlineStr">
         <is>
           <t>5/12</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="7" t="n">
         <v>0.041181</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="7" t="n">
         <v>0.08431</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" s="7" t="n">
         <v>0.08167099999999999</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="7" t="n">
         <v>0.117956</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" s="7" t="n">
         <v>0.126227</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23" s="7" t="n">
         <v>0.203195</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23" s="7" t="n">
         <v>0.190978</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W23" s="7" t="n">
         <v>0.235758</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X23" s="7" t="n">
         <v>0.823396</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23" s="7" t="n">
         <v>0.190031</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z23" s="7" t="n">
         <v>0.215191</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA23" s="7" t="n">
         <v>0.165231</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB23" s="7" t="n">
         <v>0.225912</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC23" s="7" t="n">
         <v>0.207772</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD23" s="7" t="n">
         <v>0.356275</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AE23" s="7" t="n">
         <v>69.230769</v>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF23" s="7" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="C24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="F24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="9" t="n">
         <v>0.805986</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="S24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="9" t="n">
         <v>0.061999</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AD24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AF24" s="9" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A2:AF2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>